--- a/assets/templates/rvc_train_params.xlsx
+++ b/assets/templates/rvc_train_params.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\RVC\Retrieval-based-Voice-Conversion-WebUI\assets\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{942CC48E-C605-4310-8C78-EC3AAC06169B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DD2AD3B-A8F5-4EFC-90FC-7051A2537FE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6030" yWindow="3350" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="50">
   <si>
     <t>파라미터</t>
   </si>
@@ -666,9 +666,7 @@
       <c r="D2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="5">
-        <v>20</v>
-      </c>
+      <c r="E2" s="5"/>
     </row>
     <row r="3" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="6" t="s">
@@ -683,9 +681,7 @@
       <c r="D3" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="5">
-        <v>8</v>
-      </c>
+      <c r="E3" s="5"/>
     </row>
     <row r="4" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="3" t="s">
@@ -700,9 +696,7 @@
       <c r="D4" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="5" t="s">
-        <v>16</v>
-      </c>
+      <c r="E4" s="5"/>
     </row>
     <row r="5" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="6" t="s">
@@ -717,9 +711,7 @@
       <c r="D5" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E5" s="5">
-        <v>1</v>
-      </c>
+      <c r="E5" s="5"/>
     </row>
     <row r="6" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="3" t="s">
@@ -734,9 +726,7 @@
       <c r="D6" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E6" s="5" t="s">
-        <v>24</v>
-      </c>
+      <c r="E6" s="5"/>
     </row>
     <row r="7" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" s="6" t="s">
@@ -751,9 +741,7 @@
       <c r="D7" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="E7" s="5">
-        <v>0.75</v>
-      </c>
+      <c r="E7" s="5"/>
     </row>
     <row r="8" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A8" s="3" t="s">
@@ -768,9 +756,7 @@
       <c r="D8" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="E8" s="5">
-        <v>0.33</v>
-      </c>
+      <c r="E8" s="5"/>
     </row>
     <row r="9" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A9" s="6" t="s">
@@ -785,9 +771,7 @@
       <c r="D9" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="E9" s="11" t="s">
-        <v>48</v>
-      </c>
+      <c r="E9" s="11"/>
     </row>
     <row r="10" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A10" s="3" t="s">
@@ -802,9 +786,7 @@
       <c r="D10" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="E10" s="11" t="s">
-        <v>49</v>
-      </c>
+      <c r="E10" s="11"/>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
